--- a/tame_output/ON/bt/strategyON_20231215.xlsx
+++ b/tame_output/ON/bt/strategyON_20231215.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-419.4%</t>
+          <t>-436.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>532.0%</t>
+          <t>494.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-164.9%</t>
+          <t>-163.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-89.7%</t>
+          <t>-90.1%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-156.3%</t>
+          <t>-163.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.6%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-173.5%</t>
+          <t>-186.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-146.0%</t>
+          <t>-141.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-50.0%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>110.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>-100.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>105.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
     </row>
@@ -42157,16 +42157,16 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-2.615996041268082</v>
+        <v>-2.786646756881801</v>
       </c>
       <c r="E1767" t="n">
-        <v>1.986513515251159</v>
+        <v>1.918253229005672</v>
       </c>
       <c r="F1767" t="n">
-        <v>0.4428584067673121</v>
+        <v>0.3185094682134281</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.298983400132528</v>
+        <v>3.224374037000198</v>
       </c>
     </row>
     <row r="1768">
@@ -42180,16 +42180,16 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-2.614214278897491</v>
+        <v>-2.78486499451121</v>
       </c>
       <c r="E1768" t="n">
-        <v>1.98888651737627</v>
+        <v>1.920626231130783</v>
       </c>
       <c r="F1768" t="n">
-        <v>0.4428584067673121</v>
+        <v>0.3185094682134281</v>
       </c>
       <c r="G1768" t="n">
-        <v>3.300643697309402</v>
+        <v>3.226034334177072</v>
       </c>
     </row>
     <row r="1769">
@@ -42203,16 +42203,16 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-2.618291634034582</v>
+        <v>-2.788942349648301</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.002289745585124</v>
+        <v>1.934029459339637</v>
       </c>
       <c r="F1769" t="n">
-        <v>0.4428584067673121</v>
+        <v>0.3185094682134281</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.315677867573092</v>
+        <v>3.241068504440762</v>
       </c>
     </row>
     <row r="1770">
@@ -42226,16 +42226,16 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-2.608299553108173</v>
+        <v>-2.778950268721892</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.004601012619821</v>
+        <v>1.936340726374333</v>
       </c>
       <c r="F1770" t="n">
-        <v>0.4528504876937213</v>
+        <v>0.3285015491398373</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.319987550793071</v>
+        <v>3.245378187660741</v>
       </c>
     </row>
     <row r="1771">
@@ -42249,16 +42249,16 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-2.608855308164211</v>
+        <v>-2.77950602377793</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.007280520493997</v>
+        <v>1.939020234248509</v>
       </c>
       <c r="F1771" t="n">
-        <v>0.4512430739326433</v>
+        <v>0.3268941353787593</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.321924912433016</v>
+        <v>3.247315549300685</v>
       </c>
     </row>
     <row r="1772">
@@ -42272,16 +42272,16 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-2.612069660577522</v>
+        <v>-2.782720376191241</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.011519768667819</v>
+        <v>1.943259482422332</v>
       </c>
       <c r="F1772" t="n">
-        <v>0.4512430739326433</v>
+        <v>0.3268941353787593</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.327449901572163</v>
+        <v>3.252840538439832</v>
       </c>
     </row>
     <row r="1773">
@@ -42295,16 +42295,16 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-2.629077905980132</v>
+        <v>-2.799728621593851</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.005794043144507</v>
+        <v>1.93753375689902</v>
       </c>
       <c r="F1773" t="n">
-        <v>0.4542422089456171</v>
+        <v>0.3298932703917331</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.330326955217679</v>
+        <v>3.255717592085348</v>
       </c>
     </row>
     <row r="1774">
@@ -42318,16 +42318,16 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-2.610118183528777</v>
+        <v>-2.780768899142496</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.014127794296322</v>
+        <v>1.945867508050834</v>
       </c>
       <c r="F1774" t="n">
-        <v>0.4542422089456171</v>
+        <v>0.3298932703917331</v>
       </c>
       <c r="G1774" t="n">
-        <v>3.331076817388952</v>
+        <v>3.256467454256621</v>
       </c>
     </row>
     <row r="1775">
@@ -42341,16 +42341,16 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-2.608883458925969</v>
+        <v>-2.779534174539688</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.012857281601026</v>
+        <v>1.944596995355539</v>
       </c>
       <c r="F1775" t="n">
-        <v>0.4542422089456171</v>
+        <v>0.3298932703917331</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.329312414852533</v>
+        <v>3.254703051720202</v>
       </c>
     </row>
     <row r="1776">
@@ -42364,16 +42364,16 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-2.618917722749618</v>
+        <v>-2.789568438363336</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.012411185908428</v>
+        <v>1.944150899662941</v>
       </c>
       <c r="F1776" t="n">
-        <v>0.4542422089456171</v>
+        <v>0.3298932703917331</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.332880024689394</v>
+        <v>3.258270661557064</v>
       </c>
     </row>
     <row r="1777">
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-2.623956721047485</v>
+        <v>-2.794607436661203</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.03437754847889</v>
+        <v>1.966117262233403</v>
       </c>
       <c r="F1777" t="n">
-        <v>0.4492032106477504</v>
+        <v>0.3248542720938664</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.353838587600283</v>
+        <v>3.279229224467953</v>
       </c>
     </row>
     <row r="1778">
@@ -42410,16 +42410,16 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-2.614137002886934</v>
+        <v>-2.784787718500652</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.03577414723034</v>
+        <v>1.967513860984853</v>
       </c>
       <c r="F1778" t="n">
-        <v>0.4556331508644378</v>
+        <v>0.3312842123105538</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.355165263217525</v>
+        <v>3.280555900085194</v>
       </c>
     </row>
     <row r="1779">
@@ -42433,16 +42433,16 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-2.61233537604798</v>
+        <v>-2.782986091661698</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.021743359969548</v>
+        <v>1.95348307372406</v>
       </c>
       <c r="F1779" t="n">
-        <v>0.4556331508644378</v>
+        <v>0.3312842123105538</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.340413825221151</v>
+        <v>3.26580446208882</v>
       </c>
     </row>
     <row r="1780">
@@ -42456,16 +42456,16 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-2.611346694303812</v>
+        <v>-2.781997409917531</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.020252588982887</v>
+        <v>1.9519923027374</v>
       </c>
       <c r="F1780" t="n">
-        <v>0.4556331508644378</v>
+        <v>0.3312842123105538</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.338527581536823</v>
+        <v>3.263918218404493</v>
       </c>
     </row>
     <row r="1781">
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-2.603350339782273</v>
+        <v>-2.774001055395992</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.025424757247343</v>
+        <v>1.957164471001855</v>
       </c>
       <c r="F1781" t="n">
-        <v>0.4636295053859764</v>
+        <v>0.3392805668320923</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.345299020705586</v>
+        <v>3.270689657573256</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-2.598366589110364</v>
+        <v>-2.769017304724083</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.039256838107018</v>
+        <v>1.970996551861531</v>
       </c>
       <c r="F1782" t="n">
-        <v>0.4686132560578851</v>
+        <v>0.344264317504001</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.360127851699644</v>
+        <v>3.285518488567313</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-2.591980450160809</v>
+        <v>-2.762631165774528</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.048539496698629</v>
+        <v>1.980279210453142</v>
       </c>
       <c r="F1783" t="n">
-        <v>0.4686132560578851</v>
+        <v>0.344264317504001</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.366856054711433</v>
+        <v>3.292246691579102</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-2.603785800479442</v>
+        <v>-2.77443651609316</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.047833445330718</v>
+        <v>1.979573159085231</v>
       </c>
       <c r="F1784" t="n">
-        <v>0.4568079057392525</v>
+        <v>0.3324589671853684</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.363788933279795</v>
+        <v>3.289179570147465</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-2.595053989700776</v>
+        <v>-2.765704705314494</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.057273627252074</v>
+        <v>1.989013341006587</v>
       </c>
       <c r="F1785" t="n">
-        <v>0.4655397165179187</v>
+        <v>0.3411907779640347</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.374975477356884</v>
+        <v>3.300366114224554</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-2.588717103056323</v>
+        <v>-2.759367818670042</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.055119200857841</v>
+        <v>1.986858914612353</v>
       </c>
       <c r="F1786" t="n">
-        <v>0.4655397165179187</v>
+        <v>0.3411907779640347</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.37028629630487</v>
+        <v>3.29567693317254</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-2.586182655328955</v>
+        <v>-2.756833370942674</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.066095637750982</v>
+        <v>1.997835351505495</v>
       </c>
       <c r="F1787" t="n">
-        <v>0.4655397165179187</v>
+        <v>0.3411907779640347</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.380248954107063</v>
+        <v>3.305639590974733</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-2.58625855430956</v>
+        <v>-2.756909269923278</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.05847995835165</v>
+        <v>1.990219672106162</v>
       </c>
       <c r="F1788" t="n">
-        <v>0.4663029772072456</v>
+        <v>0.3419540386533615</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.373121590713569</v>
+        <v>3.298512227581239</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-2.596760743868906</v>
+        <v>-2.767411459482625</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.032043658318285</v>
+        <v>1.963783372072797</v>
       </c>
       <c r="F1789" t="n">
-        <v>0.4558007876478989</v>
+        <v>0.3314518490940149</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.344584852768335</v>
+        <v>3.269975489636004</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-2.598594006548022</v>
+        <v>-2.769244722161741</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.03201119309276</v>
+        <v>1.963750906847272</v>
       </c>
       <c r="F1790" t="n">
-        <v>0.4558007876478989</v>
+        <v>0.3314518490940149</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.345285692614457</v>
+        <v>3.270676329482126</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-2.603603121609606</v>
+        <v>-2.774253837223325</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.030524626896985</v>
+        <v>1.962264340651498</v>
       </c>
       <c r="F1791" t="n">
-        <v>0.4548062100893642</v>
+        <v>0.3304572715354802</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.345206025908195</v>
+        <v>3.270596662775865</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-2.607308678246421</v>
+        <v>-2.77795939386014</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.028270129482625</v>
+        <v>1.960009843237138</v>
       </c>
       <c r="F1792" t="n">
-        <v>0.4529365348317293</v>
+        <v>0.3285875962778453</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.34331194599398</v>
+        <v>3.268702582861649</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-2.606076352889056</v>
+        <v>-2.776727068502774</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.029182911687891</v>
+        <v>1.960922625442403</v>
       </c>
       <c r="F1793" t="n">
-        <v>0.4535669112037669</v>
+        <v>0.3292179726498828</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.344110023879521</v>
+        <v>3.269500660747191</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-2.595748355873203</v>
+        <v>-2.766399071486922</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.037444018658445</v>
+        <v>1.969183732412958</v>
       </c>
       <c r="F1794" t="n">
-        <v>0.463894908219619</v>
+        <v>0.339545969665735</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.354436730253246</v>
+        <v>3.279827367120915</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-2.595632020725648</v>
+        <v>-2.766282736339366</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.044011212919303</v>
+        <v>1.975750926673816</v>
       </c>
       <c r="F1795" t="n">
-        <v>0.4640112433671748</v>
+        <v>0.3396623048132907</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.361027191543616</v>
+        <v>3.286417828411285</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-2.597477430302515</v>
+        <v>-2.768128145916234</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.040247019533945</v>
+        <v>1.971986733288457</v>
       </c>
       <c r="F1796" t="n">
-        <v>0.4640112433671748</v>
+        <v>0.3396623048132907</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.358001161989004</v>
+        <v>3.283391798856674</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-2.595978997777416</v>
+        <v>-2.766629713391135</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.040784680405118</v>
+        <v>1.972524394159631</v>
       </c>
       <c r="F1797" t="n">
-        <v>0.4655096758922737</v>
+        <v>0.3411607373383896</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.358838509365197</v>
+        <v>3.284229146232867</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-2.60404324997015</v>
+        <v>-2.774693965583868</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.038836957471336</v>
+        <v>1.970576671225849</v>
       </c>
       <c r="F1798" t="n">
-        <v>0.4574454236995398</v>
+        <v>0.3330964851456558</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.355277935992869</v>
+        <v>3.280668572860538</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-2.605373217431362</v>
+        <v>-2.776023933045081</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.038304970486851</v>
+        <v>1.970044684241364</v>
       </c>
       <c r="F1799" t="n">
-        <v>0.4574454236995398</v>
+        <v>0.3330964851456558</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.355277935992869</v>
+        <v>3.280668572860538</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-2.377508534697851</v>
+        <v>-2.54815925031157</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.131667316687418</v>
+        <v>2.06340703044193</v>
       </c>
       <c r="F1800" t="n">
-        <v>0.4574454236995398</v>
+        <v>0.3330964851456558</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.357494409100031</v>
+        <v>3.2828850459677</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-2.129406970830634</v>
+        <v>-2.300057686444353</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.238442538579397</v>
+        <v>2.170182252333909</v>
       </c>
       <c r="F1801" t="n">
-        <v>0.4574454236995398</v>
+        <v>0.3330964851456558</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.365029005445123</v>
+        <v>3.290419642312792</v>
       </c>
     </row>
     <row r="1802">
@@ -42962,16 +42962,16 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-1.832568571437304</v>
+        <v>-2.003219287051023</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.358600909310187</v>
+        <v>2.290340623064699</v>
       </c>
       <c r="F1802" t="n">
-        <v>0.5722999121806676</v>
+        <v>0.4479509736267835</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.435364709507257</v>
+        <v>3.360755346374927</v>
       </c>
     </row>
     <row r="1803">
@@ -42985,16 +42985,16 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-1.528929014611867</v>
+        <v>-1.699579730225586</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.481733806506047</v>
+        <v>2.41347352026056</v>
       </c>
       <c r="F1803" t="n">
-        <v>0.5722999121806676</v>
+        <v>0.4479509736267835</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.437041783972943</v>
+        <v>3.362432420840613</v>
       </c>
     </row>
     <row r="1804">
@@ -43008,16 +43008,16 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-1.239908408171158</v>
+        <v>-1.410559123784877</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.593281470531788</v>
+        <v>2.525021184286301</v>
       </c>
       <c r="F1804" t="n">
-        <v>0.5722999121806676</v>
+        <v>0.4479509736267835</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.432981205422401</v>
+        <v>3.358371842290071</v>
       </c>
     </row>
     <row r="1805">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-0.9551884809072613</v>
+        <v>-1.12583919652098</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.712389580781365</v>
+        <v>2.644129294535877</v>
       </c>
       <c r="F1805" t="n">
-        <v>0.8570198394445647</v>
+        <v>0.7326709008906807</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.609033301124757</v>
+        <v>3.534423937992426</v>
       </c>
     </row>
     <row r="1806">
@@ -43054,16 +43054,16 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-0.6714268114157209</v>
+        <v>-0.8420775270294398</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.831206411751788</v>
+        <v>2.7629461255063</v>
       </c>
       <c r="F1806" t="n">
-        <v>0.8570198394445647</v>
+        <v>0.7326709008906807</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.614345464298564</v>
+        <v>3.539736101166233</v>
       </c>
     </row>
     <row r="1807">
@@ -43077,16 +43077,16 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-0.4097784170230803</v>
+        <v>-0.5804291326367992</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.929108356955478</v>
+        <v>2.860848070709991</v>
       </c>
       <c r="F1807" t="n">
-        <v>1.118668233837205</v>
+        <v>0.9943192952833213</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.764577088380782</v>
+        <v>3.689967725248451</v>
       </c>
     </row>
     <row r="1808">
@@ -43100,16 +43100,16 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-0.09561197888374784</v>
+        <v>-0.2662626944974668</v>
       </c>
       <c r="E1808" t="n">
-        <v>3.052238607227324</v>
+        <v>2.983978320981836</v>
       </c>
       <c r="F1808" t="n">
-        <v>1.432834671976538</v>
+        <v>1.308485733422654</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.950540626280493</v>
+        <v>3.875931263148163</v>
       </c>
     </row>
     <row r="1809">
@@ -43123,16 +43123,16 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>0.02689972522202455</v>
+        <v>-0.1437509903916944</v>
       </c>
       <c r="E1809" t="n">
-        <v>3.119657672496372</v>
+        <v>3.051397386250884</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.55534637608231</v>
+        <v>1.430997437528426</v>
       </c>
       <c r="G1809" t="n">
-        <v>4.042462032370696</v>
+        <v>3.967852669238366</v>
       </c>
     </row>
     <row r="1810">
@@ -43146,16 +43146,16 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>0.1882882591487529</v>
+        <v>0.01763754353503399</v>
       </c>
       <c r="E1810" t="n">
-        <v>3.194029210122542</v>
+        <v>3.125768923877054</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.716734910009039</v>
+        <v>1.592385971455155</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.149111276782212</v>
+        <v>4.074501913649882</v>
       </c>
     </row>
     <row r="1811">
@@ -43169,16 +43169,16 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>0.3680344502972591</v>
+        <v>0.1973837346835402</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.279455298633876</v>
+        <v>3.211195012388388</v>
       </c>
       <c r="F1811" t="n">
-        <v>1.716734910009039</v>
+        <v>1.592385971455155</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.162638888834143</v>
+        <v>4.088029525701813</v>
       </c>
     </row>
     <row r="1812">
@@ -43186,22 +43186,22 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.09386743355499</v>
+        <v>3.09267006654491</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>0.5274679162963025</v>
+        <v>0.5232365538489198</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.349816065284759</v>
+        <v>3.348123520305806</v>
       </c>
       <c r="F1812" t="n">
-        <v>1.716734910009039</v>
+        <v>1.592385971455155</v>
       </c>
       <c r="G1812" t="n">
-        <v>4.169226269085409</v>
+        <v>4.094616905953079</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231215.xlsx
+++ b/tame_output/ON/bt/strategyON_20231215.xlsx
@@ -43192,10 +43192,10 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>0.5232365538489198</v>
+        <v>0.5234280422152511</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.348123520305806</v>
+        <v>3.348200115652338</v>
       </c>
       <c r="F1812" t="n">
         <v>1.592385971455155</v>

--- a/tame_output/ON/bt/strategyON_20231215.xlsx
+++ b/tame_output/ON/bt/strategyON_20231215.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.4%</t>
+          <t>487.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-90.1%</t>
+          <t>-106.8%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-14.3%</t>
         </is>
       </c>
     </row>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714844</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963481</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583696</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742726</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589526</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872959</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946331</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336487</v>
+        <v>3.300520058336486</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308505</v>
+        <v>3.311781349308504</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257518</v>
+        <v>3.271427670257517</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.252962387441542</v>
+        <v>3.252962387441541</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.24125754066217</v>
+        <v>3.241257540662169</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543326</v>
+        <v>3.285495323543325</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,16 +43186,16 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.09267006654491</v>
+        <v>3.092670066544909</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>0.5234280422152511</v>
+        <v>0.3561846611547631</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.348200115652338</v>
+        <v>3.281302763228143</v>
       </c>
       <c r="F1812" t="n">
         <v>1.592385971455155</v>
